--- a/docs/downloads/04/tbl_other_act_all_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_alaotra_avaradrano.xlsx
@@ -387,12 +387,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +447,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -495,12 +477,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +489,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +501,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +513,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -585,12 +543,6 @@
           <t>Ouvrier agricole (salarié agricole) - Mpanao saraka an- tsaha</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -603,12 +555,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +567,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -652,12 +592,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +604,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +616,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +628,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +640,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +652,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +664,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -796,12 +694,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +706,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -832,12 +718,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -868,12 +748,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -922,12 +796,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -958,12 +826,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -976,12 +838,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1012,12 +868,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1030,12 +880,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1084,12 +928,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1120,12 +958,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1174,12 +1006,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1192,12 +1018,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="D47">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1210,12 +1030,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1228,12 +1042,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-      <c r="D49">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1263,12 +1071,6 @@
         <is>
           <t>Taxi-bicyclette</t>
         </is>
-      </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>0.1</v>
       </c>
     </row>
     <row r="52">
